--- a/DS_HS2026_LNW_I_Example/AP02/cinema_data.xlsx
+++ b/DS_HS2026_LNW_I_Example/AP02/cinema_data.xlsx
@@ -7,12 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="movies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cinemas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="staff" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="screenings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="customers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="tickets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ER-Diagram" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="movies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cinemas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="staff" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="screenings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="customers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tickets" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +36,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +63,11 @@
         <fgColor rgb="00EAF0FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00457B9D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,12 +81,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -145,6 +163,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="17145000" cy="10439400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -436,6 +484,873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: movies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>movieid</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung des Films</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Titel des Films</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Genre des Films (z.B. Sci-Fi, Drama)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>duration_min</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Filmdauer in Minuten</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ganzzahl (Integer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>release_year</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Erscheinungsjahr des Films</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ganzzahl (Integer)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>director</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Name des Regisseurs / der Regisseurin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>age_rating</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Altersfreigabe in Jahren (z.B. 6, 12, 16, 18)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Ganzzahl (Integer)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: cinemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cinemaid</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung des Kinos</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Name des Kinos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Stadt, in der das Kino liegt</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_seats</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gesamtanzahl Sitzplätze im Kino</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ganzzahl (Integer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>staffid</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung des Mitarbeitenden</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vorname des Mitarbeitenden</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>lastname</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Nachname des Mitarbeitenden</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cinemaid</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kino, dem der Mitarbeitende zugeordnet ist</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Foreign-Key → cinemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Rolle / Funktion (z.B. Kassier:in, Manager:in)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Einstellungsdatum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Datum (Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: screenings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>screeningid</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung der Vorstellung</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>movieid</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gezeigter Film</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Foreign-Key → movies</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>cinemaid</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Kino, in dem die Vorstellung stattfindet</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Foreign-Key → cinemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>screening_datetime</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Datum und Uhrzeit der Vorstellung</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Datum/Zeit (DateTime)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>base_price</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Basispreis des Tickets für diese Vorstellung</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Dezimalzahl (Float)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>customerid</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung des Kunden / der Kundin</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vorname</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>lastname</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Nachname</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>E-Mail-Adresse (eindeutig)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>birthdate</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Geburtsdatum</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Datum (Date)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>membership_type</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mitgliedschaftstyp (Standard, Premium, Student, Senior)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Tabelle: tickets</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Spalte</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Datentyp</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>Primary-Key / Foreign-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ticketid</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Eindeutige Kennung des Tickets</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Primary-Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>screeningid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vorstellung, für die das Ticket gilt</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Foreign-Key → screenings</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>customerid</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Kunde / Kundin, dem/der das Ticket gehört</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Foreign-Key → customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>purchase_datetime</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kaufzeitpunkt des Tickets</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Datum/Zeit (DateTime)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>seat_number</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Platznummer (z.B. A1, C12)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Zeichenkette (String)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>paid_price</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tatsächlich bezahlter Preis in CHF</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dezimalzahl (Float)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ER (Entity-Relationship) Diagram Cinema DB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -955,7 +1870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1097,7 +2012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2111,7 +3026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9659,7 +10574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25713,7 +26628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/DS_HS2026_LNW_I_Example/AP02/cinema_data.xlsx
+++ b/DS_HS2026_LNW_I_Example/AP02/cinema_data.xlsx
@@ -174,7 +174,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="17145000" cy="10439400"/>
+    <ext cx="18097500" cy="8172450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
